--- a/data/2025/xlsx_backups/Advertising Framework (respostas).xlsx
+++ b/data/2025/xlsx_backups/Advertising Framework (respostas).xlsx
@@ -601,7 +601,8 @@
     <t>There is no reference to the quota or rate limits on documentation. /api/ads</t>
   </si>
   <si>
-    <t xml:space="preserve">Although the data retrieved by the API is similar to what is displayed on the GUI, the platform does not offer enough information and manners to compare properly. The only fields about advertisers in response schema are: advertiserName, advertiserUrl and adPayer, which are insufficient to compare data from API and GUI based on the OC's requirements. </t>
+    <t>Although the data retrieved by the API is similar to what is displayed on the GUI, the platform does not offer enough information and manners to properly compare. The only relevant fields are about advertisers in response schema: advertiserName, advertiserUrl and adPayer, which are insufficient to compare data from API and GUI based on the OC's requirements.
+The GUI search page shows a preview of each ad's media and text, while the API returns no information whatsoever about each ad's content, only its URL and advertiser data</t>
   </si>
   <si>
     <t xml:space="preserve">The results returned by the platform are reproducible from both API and GUI. However, it is important to mention that the lack of information provided makes it hard to properly verify the criteria. </t>
